--- a/lib/users.xlsx
+++ b/lib/users.xlsx
@@ -32,8 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="167" formatCode="yyyy;@"/>
   </numFmts>
   <fonts count="1">
     <font>
